--- a/output/yearly_benthic_cover_iteration_20_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_20_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>44.94188010750964</v>
+        <v>45.88060662323066</v>
       </c>
       <c r="M2" t="n">
-        <v>100.6791295566811</v>
+        <v>99.23343646552982</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.04567209065105</v>
+        <v>88.10305524396432</v>
       </c>
       <c r="C3" t="n">
-        <v>45.91920157223419</v>
+        <v>45.95311659209279</v>
       </c>
       <c r="D3" t="n">
-        <v>2.22878490294661</v>
+        <v>2.228906254522792</v>
       </c>
       <c r="E3" t="n">
-        <v>5.702003169690452</v>
+        <v>5.724483575886522</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429283009822035</v>
+        <v>0.7429687515075976</v>
       </c>
       <c r="G3" t="n">
-        <v>33.96962663452982</v>
+        <v>33.9808034959709</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17470184518135</v>
+        <v>34.17656256934949</v>
       </c>
       <c r="I3" t="n">
-        <v>6.584325356181851</v>
+        <v>6.605775899804535</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643301881138772</v>
+        <v>4.643554696922484</v>
       </c>
       <c r="K3" t="n">
-        <v>11.95432790934892</v>
+        <v>11.89694475603569</v>
       </c>
       <c r="L3" t="n">
-        <v>48.89013275975828</v>
+        <v>48.91284385664985</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7636622413414</v>
+        <v>106.7629052047783</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.22517331916696</v>
+        <v>87.26957394468867</v>
       </c>
       <c r="C4" t="n">
-        <v>42.73733386946799</v>
+        <v>42.76114965358502</v>
       </c>
       <c r="D4" t="n">
-        <v>2.189732114269581</v>
+        <v>2.189207706178825</v>
       </c>
       <c r="E4" t="n">
-        <v>6.518503827760854</v>
+        <v>6.541928103271362</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444893820226516</v>
+        <v>0.7445342157086671</v>
       </c>
       <c r="G4" t="n">
-        <v>33.37441053779387</v>
+        <v>33.37557904222174</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24651157304196</v>
+        <v>34.24857392259868</v>
       </c>
       <c r="I4" t="n">
-        <v>5.498467246636457</v>
+        <v>5.51641210653022</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653058637641572</v>
+        <v>4.653338848179168</v>
       </c>
       <c r="K4" t="n">
-        <v>12.77482668083305</v>
+        <v>12.73042605531134</v>
       </c>
       <c r="L4" t="n">
-        <v>44.30494152313834</v>
+        <v>44.32493051610908</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81710207343937</v>
+        <v>99.81650622500544</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.20391685328951</v>
+        <v>86.31568198667264</v>
       </c>
       <c r="C5" t="n">
-        <v>42.56955540244679</v>
+        <v>42.66352545749377</v>
       </c>
       <c r="D5" t="n">
-        <v>2.140384276389893</v>
+        <v>2.143418206744109</v>
       </c>
       <c r="E5" t="n">
-        <v>7.136634202731234</v>
+        <v>7.172627965278524</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458108018270354</v>
+        <v>0.745858315850474</v>
       </c>
       <c r="G5" t="n">
-        <v>32.62228428919174</v>
+        <v>32.67749495756691</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30729688404362</v>
+        <v>34.3094825291218</v>
       </c>
       <c r="I5" t="n">
-        <v>4.590188887687026</v>
+        <v>4.605185538045358</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661317511418971</v>
+        <v>4.661614474065462</v>
       </c>
       <c r="K5" t="n">
-        <v>13.7960831467105</v>
+        <v>13.68431801332736</v>
       </c>
       <c r="L5" t="n">
-        <v>43.48162624954725</v>
+        <v>43.49892285955303</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84726479870453</v>
+        <v>99.84676633037415</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.87228158254763</v>
+        <v>85.16524642736249</v>
       </c>
       <c r="C6" t="n">
-        <v>41.95100453379901</v>
+        <v>42.22857298863617</v>
       </c>
       <c r="D6" t="n">
-        <v>2.075477039612373</v>
+        <v>2.087834132150812</v>
       </c>
       <c r="E6" t="n">
-        <v>7.558700935057567</v>
+        <v>7.627195453397074</v>
       </c>
       <c r="F6" t="n">
-        <v>0.746932933414665</v>
+        <v>0.7469803120332174</v>
       </c>
       <c r="G6" t="n">
-        <v>31.63301224400855</v>
+        <v>31.83008761935896</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35891493707458</v>
+        <v>34.361094353528</v>
       </c>
       <c r="I6" t="n">
-        <v>3.830912659538242</v>
+        <v>3.843427606686822</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668330833841656</v>
+        <v>4.668626950207607</v>
       </c>
       <c r="K6" t="n">
-        <v>15.12771841745236</v>
+        <v>14.83475357263752</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79377180186844</v>
+        <v>42.80875161822506</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87249475311982</v>
+        <v>99.87207817949874</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.48113186457927</v>
+        <v>83.83948969653906</v>
       </c>
       <c r="C7" t="n">
-        <v>41.15504463683845</v>
+        <v>41.50015017593427</v>
       </c>
       <c r="D7" t="n">
-        <v>2.008070770268421</v>
+        <v>2.02378583480054</v>
       </c>
       <c r="E7" t="n">
-        <v>7.845963662212132</v>
+        <v>7.927706687432972</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478862715861248</v>
+        <v>0.7479327355716839</v>
       </c>
       <c r="G7" t="n">
-        <v>30.6056516407429</v>
+        <v>30.85363892301078</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40276849296173</v>
+        <v>34.40490583629746</v>
       </c>
       <c r="I7" t="n">
-        <v>3.196501829394689</v>
+        <v>3.206940082102608</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674289197413279</v>
+        <v>4.674579597323024</v>
       </c>
       <c r="K7" t="n">
-        <v>16.51886813542072</v>
+        <v>16.16051030346092</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21967298719811</v>
+        <v>42.23257764264129</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89358575945727</v>
+        <v>99.89323812203649</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.37372684706772</v>
+        <v>88.73045015967044</v>
       </c>
       <c r="C8" t="n">
-        <v>43.49242479678061</v>
+        <v>43.80704325252624</v>
       </c>
       <c r="D8" t="n">
-        <v>2.01233421793127</v>
+        <v>2.028094653422502</v>
       </c>
       <c r="E8" t="n">
-        <v>9.701809593510147</v>
+        <v>9.765295732545743</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494741508700031</v>
+        <v>0.7495251503635998</v>
       </c>
       <c r="G8" t="n">
-        <v>31.12114804056458</v>
+        <v>31.35739677683004</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47581094002013</v>
+        <v>34.47815691672559</v>
       </c>
       <c r="I8" t="n">
-        <v>5.628936461234074</v>
+        <v>5.667448740010478</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684213442937519</v>
+        <v>4.684532189772497</v>
       </c>
       <c r="K8" t="n">
-        <v>11.62627315293227</v>
+        <v>11.26954984032954</v>
       </c>
       <c r="L8" t="n">
-        <v>44.69406836125769</v>
+        <v>44.73489331122409</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81276631097057</v>
+        <v>99.81148640407989</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.45857746977251</v>
+        <v>86.97131829056464</v>
       </c>
       <c r="C9" t="n">
-        <v>42.45141335630771</v>
+        <v>42.92832610239085</v>
       </c>
       <c r="D9" t="n">
-        <v>1.925846402336825</v>
+        <v>1.948942977740315</v>
       </c>
       <c r="E9" t="n">
-        <v>10.06805011246478</v>
+        <v>10.17275271026077</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508320219737916</v>
+        <v>0.7508843463946441</v>
       </c>
       <c r="G9" t="n">
-        <v>29.78359680835087</v>
+        <v>30.13359270253359</v>
       </c>
       <c r="H9" t="n">
-        <v>34.5382730107944</v>
+        <v>34.54067993415362</v>
       </c>
       <c r="I9" t="n">
-        <v>4.699278976515639</v>
+        <v>4.731438454515166</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692700137336197</v>
+        <v>4.693027164966524</v>
       </c>
       <c r="K9" t="n">
-        <v>13.54142253022751</v>
+        <v>13.02868170943536</v>
       </c>
       <c r="L9" t="n">
-        <v>43.85080476731938</v>
+        <v>43.88556305650682</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84364065385459</v>
+        <v>99.84257086833303</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.28453545021682</v>
+        <v>84.94100834495509</v>
       </c>
       <c r="C10" t="n">
-        <v>41.00696096119778</v>
+        <v>41.63300702111354</v>
       </c>
       <c r="D10" t="n">
-        <v>1.828459887072411</v>
+        <v>1.858174025502645</v>
       </c>
       <c r="E10" t="n">
-        <v>10.21261734771674</v>
+        <v>10.3571353629865</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519966755120734</v>
+        <v>0.7520479869135352</v>
       </c>
       <c r="G10" t="n">
-        <v>28.27749502282628</v>
+        <v>28.73016804208663</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59184707355536</v>
+        <v>34.59420739802262</v>
       </c>
       <c r="I10" t="n">
-        <v>3.922140221583511</v>
+        <v>3.948975611233578</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699979221950458</v>
+        <v>4.700299918209594</v>
       </c>
       <c r="K10" t="n">
-        <v>15.71546454978317</v>
+        <v>15.05899165504491</v>
       </c>
       <c r="L10" t="n">
-        <v>43.14703896189363</v>
+        <v>43.17657247788279</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86946447287458</v>
+        <v>99.86857115404123</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.04558002267956</v>
+        <v>82.73091871954672</v>
       </c>
       <c r="C11" t="n">
-        <v>39.37635520303238</v>
+        <v>40.03590462697451</v>
       </c>
       <c r="D11" t="n">
-        <v>1.729218786698326</v>
+        <v>1.760210354709067</v>
       </c>
       <c r="E11" t="n">
-        <v>10.20378552008877</v>
+        <v>10.36030010418476</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529965797968217</v>
+        <v>0.7530464588761653</v>
       </c>
       <c r="G11" t="n">
-        <v>26.74271171052665</v>
+        <v>27.2155022006255</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63784267065378</v>
+        <v>34.6401371083036</v>
       </c>
       <c r="I11" t="n">
-        <v>3.272796131185063</v>
+        <v>3.295182124871604</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706228623730135</v>
+        <v>4.706540367976031</v>
       </c>
       <c r="K11" t="n">
-        <v>17.95441997732045</v>
+        <v>17.26908128045326</v>
       </c>
       <c r="L11" t="n">
-        <v>42.56027648015875</v>
+        <v>42.58532032559353</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89105166051158</v>
+        <v>99.89030623302131</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.70219352136147</v>
+        <v>80.51096519522706</v>
       </c>
       <c r="C12" t="n">
-        <v>37.53988111401264</v>
+        <v>38.32676977808572</v>
       </c>
       <c r="D12" t="n">
-        <v>1.62629932027821</v>
+        <v>1.662762128179695</v>
       </c>
       <c r="E12" t="n">
-        <v>10.05155175091418</v>
+        <v>10.24492143722412</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538564538328241</v>
+        <v>0.7539035711014475</v>
       </c>
       <c r="G12" t="n">
-        <v>25.15104173733051</v>
+        <v>25.70880590352554</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67739687630989</v>
+        <v>34.67956427066657</v>
       </c>
       <c r="I12" t="n">
-        <v>2.7304445462407</v>
+        <v>2.749110565145623</v>
       </c>
       <c r="J12" t="n">
-        <v>4.71160283645515</v>
+        <v>4.711897319384045</v>
       </c>
       <c r="K12" t="n">
-        <v>20.29780647863853</v>
+        <v>19.48903480477297</v>
       </c>
       <c r="L12" t="n">
-        <v>42.0714014037048</v>
+        <v>42.0926625803393</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90908899635599</v>
+        <v>99.90846716319798</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.25789191261582</v>
+        <v>78.2498709346534</v>
       </c>
       <c r="C13" t="n">
-        <v>35.51767606281015</v>
+        <v>36.49111969128296</v>
       </c>
       <c r="D13" t="n">
-        <v>1.519855321391317</v>
+        <v>1.56434159550835</v>
       </c>
       <c r="E13" t="n">
-        <v>9.773262020838768</v>
+        <v>10.02070831398101</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545972576796086</v>
+        <v>0.7546400255881542</v>
       </c>
       <c r="G13" t="n">
-        <v>23.50486417007025</v>
+        <v>24.18707628959741</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71147385326199</v>
+        <v>34.71344117705509</v>
       </c>
       <c r="I13" t="n">
-        <v>2.277606428876344</v>
+        <v>2.293163372997423</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716232860497553</v>
+        <v>4.716500159925962</v>
       </c>
       <c r="K13" t="n">
-        <v>22.74210808738419</v>
+        <v>21.7501290653466</v>
       </c>
       <c r="L13" t="n">
-        <v>41.66437016796562</v>
+        <v>41.6823870610053</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92415431815996</v>
+        <v>99.92363581763486</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.96588050974614</v>
+        <v>84.59040949432571</v>
       </c>
       <c r="C14" t="n">
-        <v>39.58557537066977</v>
+        <v>40.36312288345185</v>
       </c>
       <c r="D14" t="n">
-        <v>1.521722382719105</v>
+        <v>1.566212068433895</v>
       </c>
       <c r="E14" t="n">
-        <v>12.06211244616381</v>
+        <v>12.20602237780711</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555242402272494</v>
+        <v>0.7555423436882728</v>
       </c>
       <c r="G14" t="n">
-        <v>25.29484507291211</v>
+        <v>25.88360801327254</v>
       </c>
       <c r="H14" t="n">
-        <v>36.51522147933113</v>
+        <v>36.42255920578208</v>
       </c>
       <c r="I14" t="n">
-        <v>3.094428386972432</v>
+        <v>3.034325837290116</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722026501420308</v>
+        <v>4.722139648051703</v>
       </c>
       <c r="K14" t="n">
-        <v>16.03411949025384</v>
+        <v>15.40959050567428</v>
       </c>
       <c r="L14" t="n">
-        <v>44.27728408205985</v>
+        <v>44.12626320931233</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89697894298347</v>
+        <v>99.89897659843845</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.12733052564077</v>
+        <v>83.96979768308611</v>
       </c>
       <c r="C15" t="n">
-        <v>39.22303059645433</v>
+        <v>40.21220713603026</v>
       </c>
       <c r="D15" t="n">
-        <v>1.490159745379582</v>
+        <v>1.543250010029486</v>
       </c>
       <c r="E15" t="n">
-        <v>12.24456182845339</v>
+        <v>12.44892885545167</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563062853486815</v>
+        <v>0.7563015006336782</v>
       </c>
       <c r="G15" t="n">
-        <v>24.7726025990541</v>
+        <v>25.50413135688851</v>
       </c>
       <c r="H15" t="n">
-        <v>36.55542625238671</v>
+        <v>36.45915601471211</v>
       </c>
       <c r="I15" t="n">
-        <v>2.581359531589061</v>
+        <v>2.531145566410161</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726914283429258</v>
+        <v>4.726884378960487</v>
       </c>
       <c r="K15" t="n">
-        <v>16.87266947435921</v>
+        <v>16.0302023169139</v>
       </c>
       <c r="L15" t="n">
-        <v>43.81834358510388</v>
+        <v>43.67330371824221</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91404365591742</v>
+        <v>99.91571317118637</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.57310770602481</v>
+        <v>81.60069321058292</v>
       </c>
       <c r="C16" t="n">
-        <v>37.06792979578493</v>
+        <v>38.2350552458349</v>
       </c>
       <c r="D16" t="n">
-        <v>1.39255548785376</v>
+        <v>1.451932378699735</v>
       </c>
       <c r="E16" t="n">
-        <v>11.80139443766198</v>
+        <v>12.06414843468811</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569799445642255</v>
+        <v>0.7569537146050568</v>
       </c>
       <c r="G16" t="n">
-        <v>23.15001717412907</v>
+        <v>23.99499359599558</v>
       </c>
       <c r="H16" t="n">
-        <v>36.58798700224443</v>
+        <v>36.49059740537119</v>
       </c>
       <c r="I16" t="n">
-        <v>2.153049006044939</v>
+        <v>2.111106964941646</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731124653526408</v>
+        <v>4.730960716281603</v>
       </c>
       <c r="K16" t="n">
-        <v>19.42689229397518</v>
+        <v>18.39930678941709</v>
       </c>
       <c r="L16" t="n">
-        <v>43.43347347880685</v>
+        <v>43.29532836568107</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92829556856697</v>
+        <v>99.92969040093304</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.15969053590402</v>
+        <v>83.13596008796111</v>
       </c>
       <c r="C17" t="n">
-        <v>38.22176118003721</v>
+        <v>39.36854765141567</v>
       </c>
       <c r="D17" t="n">
-        <v>1.393780732513329</v>
+        <v>1.453156292579033</v>
       </c>
       <c r="E17" t="n">
-        <v>12.55339928301244</v>
+        <v>12.80024129351173</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7576459759307079</v>
+        <v>0.757591792638774</v>
       </c>
       <c r="G17" t="n">
-        <v>23.55056473452962</v>
+        <v>24.39074419276426</v>
       </c>
       <c r="H17" t="n">
-        <v>37.00035800588365</v>
+        <v>36.89688123575106</v>
       </c>
       <c r="I17" t="n">
-        <v>2.168654454467344</v>
+        <v>2.102396576723924</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735287349566923</v>
+        <v>4.734948703992336</v>
       </c>
       <c r="K17" t="n">
-        <v>17.840309464096</v>
+        <v>16.86403991203888</v>
       </c>
       <c r="L17" t="n">
-        <v>43.86570442140426</v>
+        <v>43.69739157510058</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92777506553746</v>
+        <v>99.92997913855513</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.7678193341393</v>
+        <v>80.88452789528895</v>
       </c>
       <c r="C18" t="n">
-        <v>36.16472153178633</v>
+        <v>37.44230090336661</v>
       </c>
       <c r="D18" t="n">
-        <v>1.305861728463094</v>
+        <v>1.369483274488359</v>
       </c>
       <c r="E18" t="n">
-        <v>12.06296666812149</v>
+        <v>12.35541144945563</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7582185801724365</v>
+        <v>0.758139181085431</v>
       </c>
       <c r="G18" t="n">
-        <v>22.0650066779573</v>
+        <v>22.98632046318449</v>
       </c>
       <c r="H18" t="n">
-        <v>37.02832167574096</v>
+        <v>36.92354061445918</v>
       </c>
       <c r="I18" t="n">
-        <v>1.808577877606304</v>
+        <v>1.753263030831915</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738866126077728</v>
+        <v>4.738369881783941</v>
       </c>
       <c r="K18" t="n">
-        <v>20.23218066586067</v>
+        <v>19.11547210471105</v>
       </c>
       <c r="L18" t="n">
-        <v>43.54285740084003</v>
+        <v>43.38382708701334</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93975959848704</v>
+        <v>99.94160009509099</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.74913828125878</v>
+        <v>79.98256682696629</v>
       </c>
       <c r="C19" t="n">
-        <v>35.42456397372351</v>
+        <v>36.81090205417345</v>
       </c>
       <c r="D19" t="n">
-        <v>1.269129386072932</v>
+        <v>1.336650212137969</v>
       </c>
       <c r="E19" t="n">
-        <v>11.97500143832618</v>
+        <v>12.30285027713722</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7587025970146777</v>
+        <v>0.7586010967638055</v>
       </c>
       <c r="G19" t="n">
-        <v>21.44434419703</v>
+        <v>22.4352284513045</v>
       </c>
       <c r="H19" t="n">
-        <v>37.05195909613616</v>
+        <v>36.94603722555175</v>
       </c>
       <c r="I19" t="n">
-        <v>1.508110335337088</v>
+        <v>1.461942709297255</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741891231341735</v>
+        <v>4.741256854773782</v>
       </c>
       <c r="K19" t="n">
-        <v>21.25086171874124</v>
+        <v>20.01743317303372</v>
       </c>
       <c r="L19" t="n">
-        <v>43.27433603315727</v>
+        <v>43.12296302193639</v>
       </c>
       <c r="M19" t="n">
-        <v>99.94976172562201</v>
+        <v>99.95129824914356</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.19727165613298</v>
+        <v>77.57076614680538</v>
       </c>
       <c r="C20" t="n">
-        <v>33.10477076211482</v>
+        <v>34.62457695569611</v>
       </c>
       <c r="D20" t="n">
-        <v>1.176412326295763</v>
+        <v>1.247940864600885</v>
       </c>
       <c r="E20" t="n">
-        <v>11.30973503156628</v>
+        <v>11.68950204334868</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7591199481491013</v>
+        <v>0.7589984444221328</v>
       </c>
       <c r="G20" t="n">
-        <v>19.87771390336821</v>
+        <v>20.94627161002492</v>
       </c>
       <c r="H20" t="n">
-        <v>37.07234083362096</v>
+        <v>36.96538918989595</v>
       </c>
       <c r="I20" t="n">
-        <v>1.257449937200784</v>
+        <v>1.218923716874503</v>
       </c>
       <c r="J20" t="n">
-        <v>4.744499675931882</v>
+        <v>4.743740277638328</v>
       </c>
       <c r="K20" t="n">
-        <v>23.80272834386702</v>
+        <v>22.42923385319461</v>
       </c>
       <c r="L20" t="n">
-        <v>43.0506089402588</v>
+        <v>42.90557967140658</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95810804624065</v>
+        <v>99.95939048029729</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.19277543353712</v>
+        <v>83.03420193841592</v>
       </c>
       <c r="C21" t="n">
-        <v>36.76046908031788</v>
+        <v>37.91278032524393</v>
       </c>
       <c r="D21" t="n">
-        <v>1.177315341704607</v>
+        <v>1.248878791531273</v>
       </c>
       <c r="E21" t="n">
-        <v>13.29628456645831</v>
+        <v>13.49056721081605</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7597026494648027</v>
+        <v>0.7595688921904037</v>
       </c>
       <c r="G21" t="n">
-        <v>21.55538389960291</v>
+        <v>22.44225990402748</v>
       </c>
       <c r="H21" t="n">
-        <v>38.76320944459327</v>
+        <v>38.473417126325</v>
       </c>
       <c r="I21" t="n">
-        <v>1.892737972558227</v>
+        <v>1.872204437335693</v>
       </c>
       <c r="J21" t="n">
-        <v>4.748141559155016</v>
+        <v>4.747305576190021</v>
       </c>
       <c r="K21" t="n">
-        <v>17.80722456646288</v>
+        <v>16.96579806158407</v>
       </c>
       <c r="L21" t="n">
-        <v>45.36926347924742</v>
+        <v>45.05906166705924</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93695712602818</v>
+        <v>99.93764005388724</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_20_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_20_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.88060662323066</v>
+        <v>45.43256105361463</v>
       </c>
       <c r="M2" t="n">
-        <v>99.23343646552982</v>
+        <v>100.3522472542241</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.10305524396432</v>
+        <v>87.97460337434069</v>
       </c>
       <c r="C3" t="n">
-        <v>45.95311659209279</v>
+        <v>45.89843801735091</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228906254522792</v>
+        <v>2.228618291060461</v>
       </c>
       <c r="E3" t="n">
-        <v>5.724483575886522</v>
+        <v>5.686211572123425</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429687515075976</v>
+        <v>0.7428727636868205</v>
       </c>
       <c r="G3" t="n">
-        <v>33.9808034959709</v>
+        <v>33.96317174670142</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17656256934949</v>
+        <v>34.17214712959374</v>
       </c>
       <c r="I3" t="n">
-        <v>6.605775899804535</v>
+        <v>6.53862709813218</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643554696922484</v>
+        <v>4.642954773042628</v>
       </c>
       <c r="K3" t="n">
-        <v>11.89694475603569</v>
+        <v>12.02539662565935</v>
       </c>
       <c r="L3" t="n">
-        <v>48.91284385664985</v>
+        <v>48.84145034547394</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7629052047783</v>
+        <v>106.7652849884842</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.26957394468867</v>
+        <v>86.95974694419054</v>
       </c>
       <c r="C4" t="n">
-        <v>42.76114965358502</v>
+        <v>42.5141605959404</v>
       </c>
       <c r="D4" t="n">
-        <v>2.189207706178825</v>
+        <v>2.179162265533094</v>
       </c>
       <c r="E4" t="n">
-        <v>6.541928103271362</v>
+        <v>6.4700703348737</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445342157086671</v>
+        <v>0.7444276128917364</v>
       </c>
       <c r="G4" t="n">
-        <v>33.37557904222174</v>
+        <v>33.20948346565624</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24857392259868</v>
+        <v>34.24367019301987</v>
       </c>
       <c r="I4" t="n">
-        <v>5.51641210653022</v>
+        <v>5.46026049164256</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653338848179168</v>
+        <v>4.652672580573352</v>
       </c>
       <c r="K4" t="n">
-        <v>12.73042605531134</v>
+        <v>13.04025305580944</v>
       </c>
       <c r="L4" t="n">
-        <v>44.32493051610908</v>
+        <v>44.26395781774652</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81650622500544</v>
+        <v>99.81837146949636</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.31568198667264</v>
+        <v>85.55427024782807</v>
       </c>
       <c r="C5" t="n">
-        <v>42.66352545749377</v>
+        <v>41.95603649532042</v>
       </c>
       <c r="D5" t="n">
-        <v>2.143418206744109</v>
+        <v>2.109733449066687</v>
       </c>
       <c r="E5" t="n">
-        <v>7.172627965278524</v>
+        <v>7.023648162946492</v>
       </c>
       <c r="F5" t="n">
-        <v>0.745858315850474</v>
+        <v>0.7457497066692315</v>
       </c>
       <c r="G5" t="n">
-        <v>32.67749495756691</v>
+        <v>32.15141855284573</v>
       </c>
       <c r="H5" t="n">
-        <v>34.3094825291218</v>
+        <v>34.30448650678464</v>
       </c>
       <c r="I5" t="n">
-        <v>4.605185538045358</v>
+        <v>4.558298202832595</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661614474065462</v>
+        <v>4.660935666682696</v>
       </c>
       <c r="K5" t="n">
-        <v>13.68431801332736</v>
+        <v>14.44572975217192</v>
       </c>
       <c r="L5" t="n">
-        <v>43.49892285955303</v>
+        <v>43.44655984996202</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84676633037415</v>
+        <v>99.84832609745436</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>85.16524642736249</v>
+        <v>83.90671827147109</v>
       </c>
       <c r="C6" t="n">
-        <v>42.22857298863617</v>
+        <v>41.01609486778679</v>
       </c>
       <c r="D6" t="n">
-        <v>2.087834132150812</v>
+        <v>2.028601604421028</v>
       </c>
       <c r="E6" t="n">
-        <v>7.627195453397074</v>
+        <v>7.387600756357486</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469803120332174</v>
+        <v>0.7468767807308526</v>
       </c>
       <c r="G6" t="n">
-        <v>31.83008761935896</v>
+        <v>30.91500458959317</v>
       </c>
       <c r="H6" t="n">
-        <v>34.361094353528</v>
+        <v>34.35633191361921</v>
       </c>
       <c r="I6" t="n">
-        <v>3.843427606686822</v>
+        <v>3.804322747181515</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668626950207607</v>
+        <v>4.667979879567828</v>
       </c>
       <c r="K6" t="n">
-        <v>14.83475357263752</v>
+        <v>16.09328172852891</v>
       </c>
       <c r="L6" t="n">
-        <v>42.80875161822506</v>
+        <v>42.76400400916117</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87207817949874</v>
+        <v>99.87338060547687</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.83948969653906</v>
+        <v>82.04390092315491</v>
       </c>
       <c r="C7" t="n">
-        <v>41.50015017593427</v>
+        <v>39.74364454211711</v>
       </c>
       <c r="D7" t="n">
-        <v>2.02378583480054</v>
+        <v>1.9374000196959</v>
       </c>
       <c r="E7" t="n">
-        <v>7.927706687432972</v>
+        <v>7.584529651852566</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479327355716839</v>
+        <v>0.7478400268281328</v>
       </c>
       <c r="G7" t="n">
-        <v>30.85363892301078</v>
+        <v>29.52513217491557</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40490583629746</v>
+        <v>34.4006412340941</v>
       </c>
       <c r="I7" t="n">
-        <v>3.206940082102608</v>
+        <v>3.174357648092807</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674579597323024</v>
+        <v>4.674000167675829</v>
       </c>
       <c r="K7" t="n">
-        <v>16.16051030346092</v>
+        <v>17.9560990768451</v>
       </c>
       <c r="L7" t="n">
-        <v>42.23257764264129</v>
+        <v>42.19458074917164</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89323812203649</v>
+        <v>99.89432436813384</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.73045015967044</v>
+        <v>86.96320181122691</v>
       </c>
       <c r="C8" t="n">
-        <v>43.80704325252624</v>
+        <v>42.08171367813264</v>
       </c>
       <c r="D8" t="n">
-        <v>2.028094653422502</v>
+        <v>1.941582163111492</v>
       </c>
       <c r="E8" t="n">
-        <v>9.765295732545743</v>
+        <v>9.441604011494599</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495251503635998</v>
+        <v>0.7494543419991453</v>
       </c>
       <c r="G8" t="n">
-        <v>31.35739677683004</v>
+        <v>30.03991230676672</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47815691672559</v>
+        <v>34.47489973196068</v>
       </c>
       <c r="I8" t="n">
-        <v>5.667448740010478</v>
+        <v>5.631659618399642</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684532189772497</v>
+        <v>4.684089637494657</v>
       </c>
       <c r="K8" t="n">
-        <v>11.26954984032954</v>
+        <v>13.03679818877306</v>
       </c>
       <c r="L8" t="n">
-        <v>44.73489331122409</v>
+        <v>44.69417049659997</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81148640407989</v>
+        <v>99.81268236350569</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.97131829056464</v>
+        <v>84.75720697228259</v>
       </c>
       <c r="C9" t="n">
-        <v>42.92832610239085</v>
+        <v>40.74873293142754</v>
       </c>
       <c r="D9" t="n">
-        <v>1.948942977740315</v>
+        <v>1.841581820144625</v>
       </c>
       <c r="E9" t="n">
-        <v>10.17275271026077</v>
+        <v>9.738939576457829</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508843463946441</v>
+        <v>0.7508401553823867</v>
       </c>
       <c r="G9" t="n">
-        <v>30.13359270253359</v>
+        <v>28.49271971793637</v>
       </c>
       <c r="H9" t="n">
-        <v>34.54067993415362</v>
+        <v>34.53864714758978</v>
       </c>
       <c r="I9" t="n">
-        <v>4.731438454515166</v>
+        <v>4.701727583631686</v>
       </c>
       <c r="J9" t="n">
-        <v>4.693027164966524</v>
+        <v>4.692750971139916</v>
       </c>
       <c r="K9" t="n">
-        <v>13.02868170943536</v>
+        <v>15.24279302771742</v>
       </c>
       <c r="L9" t="n">
-        <v>43.88556305650682</v>
+        <v>43.85203905145504</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84257086833303</v>
+        <v>99.84356501059999</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.94100834495509</v>
+        <v>82.43557042256045</v>
       </c>
       <c r="C10" t="n">
-        <v>41.63300702111354</v>
+        <v>39.15546244014794</v>
       </c>
       <c r="D10" t="n">
-        <v>1.858174025502645</v>
+        <v>1.737643050330646</v>
       </c>
       <c r="E10" t="n">
-        <v>10.3571353629865</v>
+        <v>9.84332834302703</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520479869135352</v>
+        <v>0.7520316069919526</v>
       </c>
       <c r="G10" t="n">
-        <v>28.73016804208663</v>
+        <v>26.88459228979733</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59420739802262</v>
+        <v>34.59345392162982</v>
       </c>
       <c r="I10" t="n">
-        <v>3.948975611233578</v>
+        <v>3.924323667083971</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700299918209594</v>
+        <v>4.700197543699703</v>
       </c>
       <c r="K10" t="n">
-        <v>15.05899165504491</v>
+        <v>17.56442957743953</v>
       </c>
       <c r="L10" t="n">
-        <v>43.17657247788279</v>
+        <v>43.14950443842277</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86857115404123</v>
+        <v>99.86939645601026</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.73091871954672</v>
+        <v>80.04758933398638</v>
       </c>
       <c r="C11" t="n">
-        <v>40.03590462697451</v>
+        <v>37.37465915533451</v>
       </c>
       <c r="D11" t="n">
-        <v>1.760210354709067</v>
+        <v>1.63199086161661</v>
       </c>
       <c r="E11" t="n">
-        <v>10.36030010418476</v>
+        <v>9.790622412057425</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530464588761653</v>
+        <v>0.7530571219077802</v>
       </c>
       <c r="G11" t="n">
-        <v>27.2155022006255</v>
+        <v>25.2499550623408</v>
       </c>
       <c r="H11" t="n">
-        <v>34.6401371083036</v>
+        <v>34.64062760775789</v>
       </c>
       <c r="I11" t="n">
-        <v>3.295182124871604</v>
+        <v>3.274729256382243</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706540367976031</v>
+        <v>4.706607011923626</v>
       </c>
       <c r="K11" t="n">
-        <v>17.26908128045326</v>
+        <v>19.95241066601364</v>
       </c>
       <c r="L11" t="n">
-        <v>42.58532032559353</v>
+        <v>42.5639211878995</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89030623302131</v>
+        <v>99.89099100924764</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>80.51096519522706</v>
+        <v>77.64223377199905</v>
       </c>
       <c r="C12" t="n">
-        <v>38.32676977808572</v>
+        <v>35.47509340376617</v>
       </c>
       <c r="D12" t="n">
-        <v>1.662762128179695</v>
+        <v>1.526737207523125</v>
       </c>
       <c r="E12" t="n">
-        <v>10.24492143722412</v>
+        <v>9.614542796036927</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539035711014475</v>
+        <v>0.7539404293916899</v>
       </c>
       <c r="G12" t="n">
-        <v>25.70880590352554</v>
+        <v>23.62148391184977</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67956427066657</v>
+        <v>34.68125975201773</v>
       </c>
       <c r="I12" t="n">
-        <v>2.749110565145623</v>
+        <v>2.732141991481742</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711897319384045</v>
+        <v>4.712127683698061</v>
       </c>
       <c r="K12" t="n">
-        <v>19.48903480477297</v>
+        <v>22.35776622800095</v>
       </c>
       <c r="L12" t="n">
-        <v>42.0926625803393</v>
+        <v>42.07617566666671</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90846716319798</v>
+        <v>99.90903529843384</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>78.2498709346534</v>
+        <v>75.31355507645334</v>
       </c>
       <c r="C13" t="n">
-        <v>36.49111969128296</v>
+        <v>33.56748981473939</v>
       </c>
       <c r="D13" t="n">
-        <v>1.56434159550835</v>
+        <v>1.42590141419358</v>
       </c>
       <c r="E13" t="n">
-        <v>10.02070831398101</v>
+        <v>9.359381920233815</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546400255881542</v>
+        <v>0.754700935147273</v>
       </c>
       <c r="G13" t="n">
-        <v>24.18707628959741</v>
+        <v>22.06136534125654</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71344117705509</v>
+        <v>34.71624301677455</v>
       </c>
       <c r="I13" t="n">
-        <v>2.293163372997423</v>
+        <v>2.279081604177125</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716500159925962</v>
+        <v>4.716880844670455</v>
       </c>
       <c r="K13" t="n">
-        <v>21.7501290653466</v>
+        <v>24.68644492354665</v>
       </c>
       <c r="L13" t="n">
-        <v>41.6823870610053</v>
+        <v>41.67017242861725</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92363581763486</v>
+        <v>99.92410716690328</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.59040949432571</v>
+        <v>82.57356591558333</v>
       </c>
       <c r="C14" t="n">
-        <v>40.36312288345185</v>
+        <v>38.19684327117848</v>
       </c>
       <c r="D14" t="n">
-        <v>1.566212068433895</v>
+        <v>1.427506350082789</v>
       </c>
       <c r="E14" t="n">
-        <v>12.20602237780711</v>
+        <v>11.90260304435748</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555423436882728</v>
+        <v>0.7555503954285948</v>
       </c>
       <c r="G14" t="n">
-        <v>25.88360801327254</v>
+        <v>24.15417627450711</v>
       </c>
       <c r="H14" t="n">
-        <v>36.42255920578208</v>
+        <v>36.82329775899594</v>
       </c>
       <c r="I14" t="n">
-        <v>3.034325837290116</v>
+        <v>2.788242120782699</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722139648051703</v>
+        <v>4.722189971428716</v>
       </c>
       <c r="K14" t="n">
-        <v>15.40959050567428</v>
+        <v>17.42643408441667</v>
       </c>
       <c r="L14" t="n">
-        <v>44.12626320931233</v>
+        <v>44.28388573378076</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89897659843845</v>
+        <v>99.90716308937591</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.96979768308611</v>
+        <v>81.90129454014622</v>
       </c>
       <c r="C15" t="n">
-        <v>40.21220713603026</v>
+        <v>37.95373079909587</v>
       </c>
       <c r="D15" t="n">
-        <v>1.543250010029486</v>
+        <v>1.403106745017457</v>
       </c>
       <c r="E15" t="n">
-        <v>12.44892885545167</v>
+        <v>12.08787137800098</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563015006336782</v>
+        <v>0.7562655691447893</v>
       </c>
       <c r="G15" t="n">
-        <v>25.50413135688851</v>
+        <v>23.7424125870373</v>
       </c>
       <c r="H15" t="n">
-        <v>36.45915601471211</v>
+        <v>36.85924398795693</v>
       </c>
       <c r="I15" t="n">
-        <v>2.531145566410161</v>
+        <v>2.325734465833838</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726884378960487</v>
+        <v>4.726659807154932</v>
       </c>
       <c r="K15" t="n">
-        <v>16.0302023169139</v>
+        <v>18.09870545985376</v>
       </c>
       <c r="L15" t="n">
-        <v>43.67330371824221</v>
+        <v>43.87011257102863</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91571317118637</v>
+        <v>99.92254882997827</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>81.60069321058292</v>
+        <v>79.46020832596767</v>
       </c>
       <c r="C16" t="n">
-        <v>38.2350552458349</v>
+        <v>35.87158874083222</v>
       </c>
       <c r="D16" t="n">
-        <v>1.451932378699735</v>
+        <v>1.312183460709381</v>
       </c>
       <c r="E16" t="n">
-        <v>12.06414843468811</v>
+        <v>11.62784187906376</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569537146050568</v>
+        <v>0.7568809379777747</v>
       </c>
       <c r="G16" t="n">
-        <v>23.99499359599558</v>
+        <v>22.20387096326086</v>
       </c>
       <c r="H16" t="n">
-        <v>36.49059740537119</v>
+        <v>36.88923613738566</v>
       </c>
       <c r="I16" t="n">
-        <v>2.111106964941646</v>
+        <v>1.939689085209144</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730960716281603</v>
+        <v>4.73050586236109</v>
       </c>
       <c r="K16" t="n">
-        <v>18.39930678941709</v>
+        <v>20.53979167403232</v>
       </c>
       <c r="L16" t="n">
-        <v>43.29532836568107</v>
+        <v>43.5240158499734</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92969040093304</v>
+        <v>99.93539626483795</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>83.13596008796111</v>
+        <v>81.4289953545872</v>
       </c>
       <c r="C17" t="n">
-        <v>39.36854765141567</v>
+        <v>37.30871022463062</v>
       </c>
       <c r="D17" t="n">
-        <v>1.453156292579033</v>
+        <v>1.313200066800686</v>
       </c>
       <c r="E17" t="n">
-        <v>12.80024129351173</v>
+        <v>12.49907890109596</v>
       </c>
       <c r="F17" t="n">
-        <v>0.757591792638774</v>
+        <v>0.7574673268441037</v>
       </c>
       <c r="G17" t="n">
-        <v>24.39074419276426</v>
+        <v>22.76786862440004</v>
       </c>
       <c r="H17" t="n">
-        <v>36.89688123575106</v>
+        <v>37.46461119515883</v>
       </c>
       <c r="I17" t="n">
-        <v>2.102396576723924</v>
+        <v>1.892598447511931</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734948703992336</v>
+        <v>4.734170792775646</v>
       </c>
       <c r="K17" t="n">
-        <v>16.86403991203888</v>
+        <v>18.57100464541281</v>
       </c>
       <c r="L17" t="n">
-        <v>43.69739157510058</v>
+        <v>44.05724735317058</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92997913855513</v>
+        <v>99.93696222321401</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.88452789528895</v>
+        <v>79.15276421490576</v>
       </c>
       <c r="C18" t="n">
-        <v>37.44230090336661</v>
+        <v>35.32424467494712</v>
       </c>
       <c r="D18" t="n">
-        <v>1.369483274488359</v>
+        <v>1.232303542497407</v>
       </c>
       <c r="E18" t="n">
-        <v>12.35541144945563</v>
+        <v>11.99213887781185</v>
       </c>
       <c r="F18" t="n">
-        <v>0.758139181085431</v>
+        <v>0.757970760615154</v>
       </c>
       <c r="G18" t="n">
-        <v>22.98632046318449</v>
+        <v>21.36530896569176</v>
       </c>
       <c r="H18" t="n">
-        <v>36.92354061445918</v>
+        <v>37.48951121371606</v>
       </c>
       <c r="I18" t="n">
-        <v>1.753263030831915</v>
+        <v>1.578213600728818</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738369881783941</v>
+        <v>4.737317253844711</v>
       </c>
       <c r="K18" t="n">
-        <v>19.11547210471105</v>
+        <v>20.84723578509426</v>
       </c>
       <c r="L18" t="n">
-        <v>43.38382708701334</v>
+        <v>43.77594736086108</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94160009509099</v>
+        <v>99.94742782090245</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.98256682696629</v>
+        <v>78.2905933810362</v>
       </c>
       <c r="C19" t="n">
-        <v>36.81090205417345</v>
+        <v>34.70474764618118</v>
       </c>
       <c r="D19" t="n">
-        <v>1.336650212137969</v>
+        <v>1.202260831399756</v>
       </c>
       <c r="E19" t="n">
-        <v>12.30285027713722</v>
+        <v>11.91909793905666</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7586010967638055</v>
+        <v>0.7583954284840206</v>
       </c>
       <c r="G19" t="n">
-        <v>22.4352284513045</v>
+        <v>20.84443745746945</v>
       </c>
       <c r="H19" t="n">
-        <v>36.94603722555175</v>
+        <v>37.51051544192542</v>
       </c>
       <c r="I19" t="n">
-        <v>1.461942709297255</v>
+        <v>1.315914854675762</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741256854773782</v>
+        <v>4.739971428025127</v>
       </c>
       <c r="K19" t="n">
-        <v>20.01743317303372</v>
+        <v>21.7094066189638</v>
       </c>
       <c r="L19" t="n">
-        <v>43.12296302193639</v>
+        <v>43.54200646816812</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95129824914356</v>
+        <v>99.95616073331311</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>77.57076614680538</v>
+        <v>75.83109939740302</v>
       </c>
       <c r="C20" t="n">
-        <v>34.62457695569611</v>
+        <v>32.44746362481499</v>
       </c>
       <c r="D20" t="n">
-        <v>1.247940864600885</v>
+        <v>1.115741864526773</v>
       </c>
       <c r="E20" t="n">
-        <v>11.68950204334868</v>
+        <v>11.24421133916265</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589984444221328</v>
+        <v>0.758761177391943</v>
       </c>
       <c r="G20" t="n">
-        <v>20.94627161002492</v>
+        <v>19.34439757696442</v>
       </c>
       <c r="H20" t="n">
-        <v>36.96538918989595</v>
+        <v>37.52860551676397</v>
       </c>
       <c r="I20" t="n">
-        <v>1.218923716874503</v>
+        <v>1.097124563893613</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743740277638328</v>
+        <v>4.742257358699642</v>
       </c>
       <c r="K20" t="n">
-        <v>22.42923385319461</v>
+        <v>24.168900602597</v>
       </c>
       <c r="L20" t="n">
-        <v>42.90557967140658</v>
+        <v>43.34708258218035</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95939048029729</v>
+        <v>99.96344680959233</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>83.03420193841592</v>
+        <v>81.84578652494814</v>
       </c>
       <c r="C21" t="n">
-        <v>37.91278032524393</v>
+        <v>36.25588094292262</v>
       </c>
       <c r="D21" t="n">
-        <v>1.248878791531273</v>
+        <v>1.116422771960387</v>
       </c>
       <c r="E21" t="n">
-        <v>13.49056721081605</v>
+        <v>13.27348592494174</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7595688921904037</v>
+        <v>0.7592242290551012</v>
       </c>
       <c r="G21" t="n">
-        <v>22.44225990402748</v>
+        <v>21.12887401190308</v>
       </c>
       <c r="H21" t="n">
-        <v>38.473417126325</v>
+        <v>39.32417928770326</v>
       </c>
       <c r="I21" t="n">
-        <v>1.872204437335693</v>
+        <v>1.498448867790195</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747305576190021</v>
+        <v>4.745151431594381</v>
       </c>
       <c r="K21" t="n">
-        <v>16.96579806158407</v>
+        <v>18.15421347505188</v>
       </c>
       <c r="L21" t="n">
-        <v>45.05906166705924</v>
+        <v>45.53998774995101</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93764005388724</v>
+        <v>99.9500821679255</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_20_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_20_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.43256105361463</v>
+        <v>43.91694757178306</v>
       </c>
       <c r="M2" t="n">
-        <v>100.3522472542241</v>
+        <v>95.01289580867308</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.97460337434069</v>
+        <v>81.46172250927228</v>
       </c>
       <c r="C3" t="n">
-        <v>45.89843801735091</v>
+        <v>43.21727806482784</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228618291060461</v>
+        <v>2.178991102447656</v>
       </c>
       <c r="E3" t="n">
-        <v>5.686211572123425</v>
+        <v>4.155261914795447</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428727636868205</v>
+        <v>0.7376222640240178</v>
       </c>
       <c r="G3" t="n">
-        <v>33.96317174670142</v>
+        <v>32.77565783265016</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17214712959374</v>
+        <v>33.93062414510481</v>
       </c>
       <c r="I3" t="n">
-        <v>6.53862709813218</v>
+        <v>3.073426100100074</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642954773042628</v>
+        <v>4.61013915015011</v>
       </c>
       <c r="K3" t="n">
-        <v>12.02539662565935</v>
+        <v>18.53827749072772</v>
       </c>
       <c r="L3" t="n">
-        <v>48.84145034547394</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7652849884842</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.95974694419054</v>
+        <v>88.49115521148943</v>
       </c>
       <c r="C4" t="n">
-        <v>42.5141605959404</v>
+        <v>42.80711061926672</v>
       </c>
       <c r="D4" t="n">
-        <v>2.179162265533094</v>
+        <v>2.184679946338961</v>
       </c>
       <c r="E4" t="n">
-        <v>6.4700703348737</v>
+        <v>6.529363241106863</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444276128917364</v>
+        <v>0.7395480258621779</v>
       </c>
       <c r="G4" t="n">
-        <v>33.20948346565624</v>
+        <v>33.46527891221706</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24367019301987</v>
+        <v>34.01920918966017</v>
       </c>
       <c r="I4" t="n">
-        <v>5.46026049164256</v>
+        <v>6.93090073466559</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652672580573352</v>
+        <v>4.622175161638611</v>
       </c>
       <c r="K4" t="n">
-        <v>13.04025305580944</v>
+        <v>11.50884478851056</v>
       </c>
       <c r="L4" t="n">
-        <v>44.26395781774652</v>
+        <v>45.45361616328827</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81837146949636</v>
+        <v>99.76957157106555</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.55427024782807</v>
+        <v>87.19906587308988</v>
       </c>
       <c r="C5" t="n">
-        <v>41.95603649532042</v>
+        <v>42.58940588916241</v>
       </c>
       <c r="D5" t="n">
-        <v>2.109733449066687</v>
+        <v>2.122442215495952</v>
       </c>
       <c r="E5" t="n">
-        <v>7.023648162946492</v>
+        <v>7.308108207003528</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457497066692315</v>
+        <v>0.7411844717819442</v>
       </c>
       <c r="G5" t="n">
-        <v>32.15141855284573</v>
+        <v>32.51191133770569</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30448650678464</v>
+        <v>34.09448570196943</v>
       </c>
       <c r="I5" t="n">
-        <v>4.558298202832595</v>
+        <v>5.788530990496201</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660935666682696</v>
+        <v>4.63240294863715</v>
       </c>
       <c r="K5" t="n">
-        <v>14.44572975217192</v>
+        <v>12.80093412691011</v>
       </c>
       <c r="L5" t="n">
-        <v>43.44655984996202</v>
+        <v>44.41713496352011</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84832609745436</v>
+        <v>99.80747497959263</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>83.90671827147109</v>
+        <v>85.59876961129375</v>
       </c>
       <c r="C6" t="n">
-        <v>41.01609486778679</v>
+        <v>41.88731260775987</v>
       </c>
       <c r="D6" t="n">
-        <v>2.028601604421028</v>
+        <v>2.04530335076413</v>
       </c>
       <c r="E6" t="n">
-        <v>7.387600756357486</v>
+        <v>7.847975160982769</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468767807308526</v>
+        <v>0.7425793658166535</v>
       </c>
       <c r="G6" t="n">
-        <v>30.91500458959317</v>
+        <v>31.33028579683496</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35633191361921</v>
+        <v>34.15865082756605</v>
       </c>
       <c r="I6" t="n">
-        <v>3.804322747181515</v>
+        <v>4.832854072975093</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667979879567828</v>
+        <v>4.641121036354083</v>
       </c>
       <c r="K6" t="n">
-        <v>16.09328172852891</v>
+        <v>14.40123038870626</v>
       </c>
       <c r="L6" t="n">
-        <v>42.76400400916117</v>
+        <v>43.55066447602007</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87338060547687</v>
+        <v>99.83920747248621</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.04390092315491</v>
+        <v>83.79145501492091</v>
       </c>
       <c r="C7" t="n">
-        <v>39.74364454211711</v>
+        <v>40.83005881038336</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9374000196959</v>
+        <v>1.95877183716583</v>
       </c>
       <c r="E7" t="n">
-        <v>7.584529651852566</v>
+        <v>8.188254422310017</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478400268281328</v>
+        <v>0.7437709937815873</v>
       </c>
       <c r="G7" t="n">
-        <v>29.52513217491557</v>
+        <v>30.00478214943977</v>
       </c>
       <c r="H7" t="n">
-        <v>34.4006412340941</v>
+        <v>34.213465713953</v>
       </c>
       <c r="I7" t="n">
-        <v>3.174357648092807</v>
+        <v>4.033841187135797</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674000167675829</v>
+        <v>4.648568711134919</v>
       </c>
       <c r="K7" t="n">
-        <v>17.9560990768451</v>
+        <v>16.20854498507906</v>
       </c>
       <c r="L7" t="n">
-        <v>42.19458074917164</v>
+        <v>42.82715025806605</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89432436813384</v>
+        <v>99.86575405352848</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>86.96320181122691</v>
+        <v>81.85078921263845</v>
       </c>
       <c r="C8" t="n">
-        <v>42.08171367813264</v>
+        <v>39.51516932085026</v>
       </c>
       <c r="D8" t="n">
-        <v>1.941582163111492</v>
+        <v>1.866653495559361</v>
       </c>
       <c r="E8" t="n">
-        <v>9.441604011494599</v>
+        <v>8.364195839055753</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494543419991453</v>
+        <v>0.7447905885632211</v>
       </c>
       <c r="G8" t="n">
-        <v>30.03991230676672</v>
+        <v>28.59369857174804</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47489973196068</v>
+        <v>34.26036707390816</v>
       </c>
       <c r="I8" t="n">
-        <v>5.631659618399642</v>
+        <v>3.366142465283791</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684089637494657</v>
+        <v>4.65494117852013</v>
       </c>
       <c r="K8" t="n">
-        <v>13.03679818877306</v>
+        <v>18.14921078736153</v>
       </c>
       <c r="L8" t="n">
-        <v>44.69417049659997</v>
+        <v>42.22356874770109</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81268236350569</v>
+        <v>99.8879488559129</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84.75720697228259</v>
+        <v>79.75193942034855</v>
       </c>
       <c r="C9" t="n">
-        <v>40.74873293142754</v>
+        <v>37.93800848948143</v>
       </c>
       <c r="D9" t="n">
-        <v>1.841581820144625</v>
+        <v>1.767815108984058</v>
       </c>
       <c r="E9" t="n">
-        <v>9.738939576457829</v>
+        <v>8.389384340672072</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508401553823867</v>
+        <v>0.7456648320383421</v>
       </c>
       <c r="G9" t="n">
-        <v>28.49271971793637</v>
+        <v>27.07967626403246</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53864714758978</v>
+        <v>34.30058227376372</v>
       </c>
       <c r="I9" t="n">
-        <v>4.701727583631686</v>
+        <v>2.808411400618269</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692750971139916</v>
+        <v>4.660405200239636</v>
       </c>
       <c r="K9" t="n">
-        <v>15.24279302771742</v>
+        <v>20.24806057965144</v>
       </c>
       <c r="L9" t="n">
-        <v>43.85203905145504</v>
+        <v>41.72042697349811</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84356501059999</v>
+        <v>99.90649604263099</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.43557042256045</v>
+        <v>85.02668835661595</v>
       </c>
       <c r="C10" t="n">
-        <v>39.15546244014794</v>
+        <v>41.58246434584083</v>
       </c>
       <c r="D10" t="n">
-        <v>1.737643050330646</v>
+        <v>1.769774779249097</v>
       </c>
       <c r="E10" t="n">
-        <v>9.84332834302703</v>
+        <v>10.43627729075672</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520316069919526</v>
+        <v>0.7464914214206847</v>
       </c>
       <c r="G10" t="n">
-        <v>26.88459228979733</v>
+        <v>28.67601612677141</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59345392162982</v>
+        <v>35.90492670367829</v>
       </c>
       <c r="I10" t="n">
-        <v>3.924323667083971</v>
+        <v>2.827630650860475</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700197543699703</v>
+        <v>4.665571383879278</v>
       </c>
       <c r="K10" t="n">
-        <v>17.56442957743953</v>
+        <v>14.97331164338404</v>
       </c>
       <c r="L10" t="n">
-        <v>43.14950443842277</v>
+        <v>43.35007402352199</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86939645601026</v>
+        <v>99.90585001274685</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.04758933398638</v>
+        <v>84.47957999599329</v>
       </c>
       <c r="C11" t="n">
-        <v>37.37465915533451</v>
+        <v>41.34931224614293</v>
       </c>
       <c r="D11" t="n">
-        <v>1.63199086161661</v>
+        <v>1.737845874068441</v>
       </c>
       <c r="E11" t="n">
-        <v>9.790622412057425</v>
+        <v>10.69960379715595</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530571219077802</v>
+        <v>0.7472087360762657</v>
       </c>
       <c r="G11" t="n">
-        <v>25.2499550623408</v>
+        <v>28.20438700498624</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64062760775789</v>
+        <v>35.98514961949503</v>
       </c>
       <c r="I11" t="n">
-        <v>3.274729256382243</v>
+        <v>2.435330363734723</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706607011923626</v>
+        <v>4.670054600476659</v>
       </c>
       <c r="K11" t="n">
-        <v>19.95241066601364</v>
+        <v>15.5204200040067</v>
       </c>
       <c r="L11" t="n">
-        <v>42.5639211878995</v>
+        <v>43.04916800100821</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89099100924764</v>
+        <v>99.91890025115784</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.64223377199905</v>
+        <v>82.16771141464767</v>
       </c>
       <c r="C12" t="n">
-        <v>35.47509340376617</v>
+        <v>39.41541715923778</v>
       </c>
       <c r="D12" t="n">
-        <v>1.526737207523125</v>
+        <v>1.640340800565237</v>
       </c>
       <c r="E12" t="n">
-        <v>9.614542796036927</v>
+        <v>10.43780166353614</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539404293916899</v>
+        <v>0.7478244143544226</v>
       </c>
       <c r="G12" t="n">
-        <v>23.62148391184977</v>
+        <v>26.62192743876714</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68125975201773</v>
+        <v>36.01480033674077</v>
       </c>
       <c r="I12" t="n">
-        <v>2.732141991481742</v>
+        <v>2.031114170968839</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712127683698061</v>
+        <v>4.67390258971514</v>
       </c>
       <c r="K12" t="n">
-        <v>22.35776622800095</v>
+        <v>17.8322885853523</v>
       </c>
       <c r="L12" t="n">
-        <v>42.07617566666671</v>
+        <v>42.68464618975062</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90903529843384</v>
+        <v>99.93235193434072</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.31355507645334</v>
+        <v>83.28962323862984</v>
       </c>
       <c r="C13" t="n">
-        <v>33.56748981473939</v>
+        <v>40.365269357084</v>
       </c>
       <c r="D13" t="n">
-        <v>1.42590141419358</v>
+        <v>1.641569659553558</v>
       </c>
       <c r="E13" t="n">
-        <v>9.359381920233815</v>
+        <v>11.06064303122691</v>
       </c>
       <c r="F13" t="n">
-        <v>0.754700935147273</v>
+        <v>0.7483846459556539</v>
       </c>
       <c r="G13" t="n">
-        <v>22.06136534125654</v>
+        <v>26.94491160473691</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71624301677455</v>
+        <v>36.34482116014347</v>
       </c>
       <c r="I13" t="n">
-        <v>2.279081604177125</v>
+        <v>1.871889099790497</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716880844670455</v>
+        <v>4.677404037222836</v>
       </c>
       <c r="K13" t="n">
-        <v>24.68644492354665</v>
+        <v>16.71037676137017</v>
       </c>
       <c r="L13" t="n">
-        <v>41.67017242861725</v>
+        <v>42.8620042873297</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92410716690328</v>
+        <v>99.93765040578386</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.57356591558333</v>
+        <v>80.95209177229522</v>
       </c>
       <c r="C14" t="n">
-        <v>38.19684327117848</v>
+        <v>38.31796207233154</v>
       </c>
       <c r="D14" t="n">
-        <v>1.427506350082789</v>
+        <v>1.5457782000673</v>
       </c>
       <c r="E14" t="n">
-        <v>11.90260304435748</v>
+        <v>10.67536665730058</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555503954285948</v>
+        <v>0.7488656552327831</v>
       </c>
       <c r="G14" t="n">
-        <v>24.15417627450711</v>
+        <v>25.37257966419171</v>
       </c>
       <c r="H14" t="n">
-        <v>36.82329775899594</v>
+        <v>36.36818106770987</v>
       </c>
       <c r="I14" t="n">
-        <v>2.788242120782699</v>
+        <v>1.560910182588089</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722189971428716</v>
+        <v>4.680410345204893</v>
       </c>
       <c r="K14" t="n">
-        <v>17.42643408441667</v>
+        <v>19.04790822770478</v>
       </c>
       <c r="L14" t="n">
-        <v>44.28388573378076</v>
+        <v>42.58213278052506</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90716308937591</v>
+        <v>99.94800308056138</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.90129454014622</v>
+        <v>79.90022764701111</v>
       </c>
       <c r="C15" t="n">
-        <v>37.95373079909587</v>
+        <v>37.46818295628336</v>
       </c>
       <c r="D15" t="n">
-        <v>1.403106745017457</v>
+        <v>1.501488009669573</v>
       </c>
       <c r="E15" t="n">
-        <v>12.08787137800098</v>
+        <v>10.59275455644938</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562655691447893</v>
+        <v>0.7492841608950969</v>
       </c>
       <c r="G15" t="n">
-        <v>23.7424125870373</v>
+        <v>24.6455954279283</v>
       </c>
       <c r="H15" t="n">
-        <v>36.85924398795693</v>
+        <v>36.38850552724215</v>
       </c>
       <c r="I15" t="n">
-        <v>2.325734465833838</v>
+        <v>1.339573959232251</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726659807154932</v>
+        <v>4.683026005594354</v>
       </c>
       <c r="K15" t="n">
-        <v>18.09870545985376</v>
+        <v>20.0997723529889</v>
       </c>
       <c r="L15" t="n">
-        <v>43.87011257102863</v>
+        <v>42.387417165637</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92254882997827</v>
+        <v>99.95537247490927</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.46020832596767</v>
+        <v>77.27137236691827</v>
       </c>
       <c r="C16" t="n">
-        <v>35.87158874083222</v>
+        <v>35.04631881363179</v>
       </c>
       <c r="D16" t="n">
-        <v>1.312183460709381</v>
+        <v>1.394723279114275</v>
       </c>
       <c r="E16" t="n">
-        <v>11.62784187906376</v>
+        <v>10.02568826226195</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568809379777747</v>
+        <v>0.7496451559969042</v>
       </c>
       <c r="G16" t="n">
-        <v>22.20387096326086</v>
+        <v>22.8931469646091</v>
       </c>
       <c r="H16" t="n">
-        <v>36.88923613738566</v>
+        <v>36.4060370232259</v>
       </c>
       <c r="I16" t="n">
-        <v>1.939689085209144</v>
+        <v>1.116849456729502</v>
       </c>
       <c r="J16" t="n">
-        <v>4.73050586236109</v>
+        <v>4.68528222498065</v>
       </c>
       <c r="K16" t="n">
-        <v>20.53979167403232</v>
+        <v>22.72862763308172</v>
       </c>
       <c r="L16" t="n">
-        <v>43.5240158499734</v>
+        <v>42.18784316553005</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93539626483795</v>
+        <v>99.96278961224355</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.4289953545872</v>
+        <v>82.61337578499055</v>
       </c>
       <c r="C17" t="n">
-        <v>37.30871022463062</v>
+        <v>38.62031223862468</v>
       </c>
       <c r="D17" t="n">
-        <v>1.313200066800686</v>
+        <v>1.39538894036954</v>
       </c>
       <c r="E17" t="n">
-        <v>12.49907890109596</v>
+        <v>11.90844883842315</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574673268441037</v>
+        <v>0.7500029400412498</v>
       </c>
       <c r="G17" t="n">
-        <v>22.76786862440004</v>
+        <v>24.58490388261746</v>
       </c>
       <c r="H17" t="n">
-        <v>37.46461119515883</v>
+        <v>38.10424325450907</v>
       </c>
       <c r="I17" t="n">
-        <v>1.892598447511931</v>
+        <v>1.182869553772269</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734170792775646</v>
+        <v>4.68751837525781</v>
       </c>
       <c r="K17" t="n">
-        <v>18.57100464541281</v>
+        <v>17.38662421500946</v>
       </c>
       <c r="L17" t="n">
-        <v>44.05724735317058</v>
+        <v>43.95365337058206</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93696222321401</v>
+        <v>99.9605898242162</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.15276421490576</v>
+        <v>84.2631046272069</v>
       </c>
       <c r="C18" t="n">
-        <v>35.32424467494712</v>
+        <v>39.32647223554861</v>
       </c>
       <c r="D18" t="n">
-        <v>1.232303542497407</v>
+        <v>1.396535651441757</v>
       </c>
       <c r="E18" t="n">
-        <v>11.99213887781185</v>
+        <v>12.49250729790759</v>
       </c>
       <c r="F18" t="n">
-        <v>0.757970760615154</v>
+        <v>0.7506192819446854</v>
       </c>
       <c r="G18" t="n">
-        <v>21.36530896569176</v>
+        <v>24.71912794790389</v>
       </c>
       <c r="H18" t="n">
-        <v>37.48951121371606</v>
+        <v>38.13555678751358</v>
       </c>
       <c r="I18" t="n">
-        <v>1.578213600728818</v>
+        <v>2.077387148341111</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737317253844711</v>
+        <v>4.691370512154282</v>
       </c>
       <c r="K18" t="n">
-        <v>20.84723578509426</v>
+        <v>15.73689537279312</v>
       </c>
       <c r="L18" t="n">
-        <v>43.77594736086108</v>
+        <v>44.86744301224242</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94742782090245</v>
+        <v>99.93081062058415</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.2905933810362</v>
+        <v>81.35694489057252</v>
       </c>
       <c r="C19" t="n">
-        <v>34.70474764618118</v>
+        <v>36.7411564353887</v>
       </c>
       <c r="D19" t="n">
-        <v>1.202260831399756</v>
+        <v>1.292330603899171</v>
       </c>
       <c r="E19" t="n">
-        <v>11.91909793905666</v>
+        <v>11.8490869304947</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7583954284840206</v>
+        <v>0.7511520622618869</v>
       </c>
       <c r="G19" t="n">
-        <v>20.84443745746945</v>
+        <v>22.87466525884664</v>
       </c>
       <c r="H19" t="n">
-        <v>37.51051544192542</v>
+        <v>38.16262493581543</v>
       </c>
       <c r="I19" t="n">
-        <v>1.315914854675762</v>
+        <v>1.732384710117884</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739971428025127</v>
+        <v>4.694700389136791</v>
       </c>
       <c r="K19" t="n">
-        <v>21.7094066189638</v>
+        <v>18.64305510942749</v>
       </c>
       <c r="L19" t="n">
-        <v>43.54200646816812</v>
+        <v>44.55808325661879</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95616073331311</v>
+        <v>99.94229480143497</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.83109939740302</v>
+        <v>78.30856918150096</v>
       </c>
       <c r="C20" t="n">
-        <v>32.44746362481499</v>
+        <v>33.95946813394722</v>
       </c>
       <c r="D20" t="n">
-        <v>1.115741864526773</v>
+        <v>1.183676044752568</v>
       </c>
       <c r="E20" t="n">
-        <v>11.24421133916265</v>
+        <v>11.09361479595549</v>
       </c>
       <c r="F20" t="n">
-        <v>0.758761177391943</v>
+        <v>0.7516139403707224</v>
       </c>
       <c r="G20" t="n">
-        <v>19.34439757696442</v>
+        <v>20.95144479047181</v>
       </c>
       <c r="H20" t="n">
-        <v>37.52860551676397</v>
+        <v>38.1860908649117</v>
       </c>
       <c r="I20" t="n">
-        <v>1.097124563893613</v>
+        <v>1.444541617721658</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742257358699642</v>
+        <v>4.697587127317013</v>
       </c>
       <c r="K20" t="n">
-        <v>24.168900602597</v>
+        <v>21.69143081849904</v>
       </c>
       <c r="L20" t="n">
-        <v>43.34708258218035</v>
+        <v>44.30097925005046</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96344680959233</v>
+        <v>99.95187820249672</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.84578652494814</v>
+        <v>75.37320245066525</v>
       </c>
       <c r="C21" t="n">
-        <v>36.25588094292262</v>
+        <v>31.245613620954</v>
       </c>
       <c r="D21" t="n">
-        <v>1.116422771960387</v>
+        <v>1.079687021291165</v>
       </c>
       <c r="E21" t="n">
-        <v>13.27348592494174</v>
+        <v>10.31974948858885</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7592242290551012</v>
+        <v>0.7520142874658162</v>
       </c>
       <c r="G21" t="n">
-        <v>21.12887401190308</v>
+        <v>19.1108057967832</v>
       </c>
       <c r="H21" t="n">
-        <v>39.32417928770326</v>
+        <v>38.20643068264209</v>
       </c>
       <c r="I21" t="n">
-        <v>1.498448867790195</v>
+        <v>1.204425877232777</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745151431594381</v>
+        <v>4.70008929666135</v>
       </c>
       <c r="K21" t="n">
-        <v>18.15421347505188</v>
+        <v>24.62679754933475</v>
       </c>
       <c r="L21" t="n">
-        <v>45.53998774995101</v>
+        <v>44.08746267366342</v>
       </c>
       <c r="M21" t="n">
-        <v>99.9500821679255</v>
+        <v>99.95987384395218</v>
       </c>
     </row>
   </sheetData>
